--- a/C_Properties/1.Crisis_events/0.Crisis_indicator.xlsx
+++ b/C_Properties/1.Crisis_events/0.Crisis_indicator.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15600" windowHeight="7050"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15600" windowHeight="7050" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="5" r:id="rId1"/>
@@ -5363,6 +5363,7 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -5375,7 +5376,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5915,7 +5915,7 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="B23" s="101" t="s">
+      <c r="B23" s="97" t="s">
         <v>1459</v>
       </c>
     </row>
@@ -6031,7 +6031,7 @@
     <tabColor rgb="FF7030A0"/>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:E189"/>
+  <dimension ref="A1:E191"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="10.08984375" bestFit="1" customWidth="1"/>
@@ -9266,6 +9266,40 @@
       </c>
       <c r="D189">
         <f>+Crisis_construction!I190</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4">
+      <c r="A190" s="59">
+        <v>45658</v>
+      </c>
+      <c r="B190">
+        <f>Crisis_construction!F191</f>
+        <v>0</v>
+      </c>
+      <c r="C190">
+        <f>Crisis_construction!G191</f>
+        <v>0</v>
+      </c>
+      <c r="D190">
+        <f>+Crisis_construction!I191</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4">
+      <c r="A191" s="59">
+        <v>45748</v>
+      </c>
+      <c r="B191">
+        <f>Crisis_construction!F192</f>
+        <v>0</v>
+      </c>
+      <c r="C191">
+        <f>Crisis_construction!G192</f>
+        <v>0</v>
+      </c>
+      <c r="D191">
+        <f>+Crisis_construction!I192</f>
         <v>0</v>
       </c>
     </row>
@@ -9285,7 +9319,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:I190"/>
+  <dimension ref="A1:I192"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="7" width="10" customWidth="1"/>
@@ -13897,7 +13931,76 @@
       </c>
     </row>
     <row r="190" spans="1:7">
-      <c r="A190" s="59"/>
+      <c r="A190" s="59">
+        <v>45566</v>
+      </c>
+      <c r="B190">
+        <f>'Babecky ·et al. (2012)'!B221</f>
+        <v>0</v>
+      </c>
+      <c r="D190">
+        <f>FX!F189</f>
+        <v>0</v>
+      </c>
+      <c r="E190">
+        <v>0</v>
+      </c>
+      <c r="F190">
+        <f t="shared" ref="F190:F192" si="7">+IF(SUM(B190:D190)=0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="G190">
+        <f t="shared" ref="G190:G192" si="8">+IF(SUM(B190:E190)=0,0,1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7">
+      <c r="A191" s="59">
+        <v>45658</v>
+      </c>
+      <c r="B191">
+        <f>'Babecky ·et al. (2012)'!B222</f>
+        <v>0</v>
+      </c>
+      <c r="D191">
+        <f>FX!F190</f>
+        <v>0</v>
+      </c>
+      <c r="E191">
+        <v>0</v>
+      </c>
+      <c r="F191">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G191">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7">
+      <c r="A192" s="59">
+        <v>45748</v>
+      </c>
+      <c r="B192">
+        <f>'Babecky ·et al. (2012)'!B223</f>
+        <v>0</v>
+      </c>
+      <c r="D192">
+        <f>FX!F191</f>
+        <v>0</v>
+      </c>
+      <c r="E192">
+        <v>0</v>
+      </c>
+      <c r="F192">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G192">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -24381,149 +24484,149 @@
       </c>
     </row>
     <row r="153" spans="1:11" ht="15.75" customHeight="1" thickTop="1">
-      <c r="A153" s="97" t="s">
+      <c r="A153" s="98" t="s">
         <v>336</v>
       </c>
-      <c r="B153" s="98"/>
-      <c r="C153" s="98"/>
-      <c r="D153" s="98"/>
-      <c r="E153" s="98"/>
-      <c r="F153" s="98"/>
-      <c r="G153" s="98"/>
-      <c r="H153" s="98"/>
-      <c r="I153" s="98"/>
-      <c r="J153" s="98"/>
-      <c r="K153" s="98"/>
+      <c r="B153" s="99"/>
+      <c r="C153" s="99"/>
+      <c r="D153" s="99"/>
+      <c r="E153" s="99"/>
+      <c r="F153" s="99"/>
+      <c r="G153" s="99"/>
+      <c r="H153" s="99"/>
+      <c r="I153" s="99"/>
+      <c r="J153" s="99"/>
+      <c r="K153" s="99"/>
     </row>
     <row r="154" spans="1:11">
-      <c r="A154" s="99"/>
-      <c r="B154" s="100"/>
-      <c r="C154" s="100"/>
-      <c r="D154" s="100"/>
-      <c r="E154" s="100"/>
-      <c r="F154" s="100"/>
-      <c r="G154" s="100"/>
-      <c r="H154" s="100"/>
-      <c r="I154" s="100"/>
-      <c r="J154" s="100"/>
-      <c r="K154" s="100"/>
+      <c r="A154" s="100"/>
+      <c r="B154" s="101"/>
+      <c r="C154" s="101"/>
+      <c r="D154" s="101"/>
+      <c r="E154" s="101"/>
+      <c r="F154" s="101"/>
+      <c r="G154" s="101"/>
+      <c r="H154" s="101"/>
+      <c r="I154" s="101"/>
+      <c r="J154" s="101"/>
+      <c r="K154" s="101"/>
     </row>
     <row r="155" spans="1:11">
-      <c r="A155" s="99"/>
-      <c r="B155" s="100"/>
-      <c r="C155" s="100"/>
-      <c r="D155" s="100"/>
-      <c r="E155" s="100"/>
-      <c r="F155" s="100"/>
-      <c r="G155" s="100"/>
-      <c r="H155" s="100"/>
-      <c r="I155" s="100"/>
-      <c r="J155" s="100"/>
-      <c r="K155" s="100"/>
+      <c r="A155" s="100"/>
+      <c r="B155" s="101"/>
+      <c r="C155" s="101"/>
+      <c r="D155" s="101"/>
+      <c r="E155" s="101"/>
+      <c r="F155" s="101"/>
+      <c r="G155" s="101"/>
+      <c r="H155" s="101"/>
+      <c r="I155" s="101"/>
+      <c r="J155" s="101"/>
+      <c r="K155" s="101"/>
     </row>
     <row r="156" spans="1:11">
-      <c r="A156" s="99"/>
-      <c r="B156" s="100"/>
-      <c r="C156" s="100"/>
-      <c r="D156" s="100"/>
-      <c r="E156" s="100"/>
-      <c r="F156" s="100"/>
-      <c r="G156" s="100"/>
-      <c r="H156" s="100"/>
-      <c r="I156" s="100"/>
-      <c r="J156" s="100"/>
-      <c r="K156" s="100"/>
+      <c r="A156" s="100"/>
+      <c r="B156" s="101"/>
+      <c r="C156" s="101"/>
+      <c r="D156" s="101"/>
+      <c r="E156" s="101"/>
+      <c r="F156" s="101"/>
+      <c r="G156" s="101"/>
+      <c r="H156" s="101"/>
+      <c r="I156" s="101"/>
+      <c r="J156" s="101"/>
+      <c r="K156" s="101"/>
     </row>
     <row r="157" spans="1:11">
-      <c r="A157" s="99"/>
-      <c r="B157" s="100"/>
-      <c r="C157" s="100"/>
-      <c r="D157" s="100"/>
-      <c r="E157" s="100"/>
-      <c r="F157" s="100"/>
-      <c r="G157" s="100"/>
-      <c r="H157" s="100"/>
-      <c r="I157" s="100"/>
-      <c r="J157" s="100"/>
-      <c r="K157" s="100"/>
+      <c r="A157" s="100"/>
+      <c r="B157" s="101"/>
+      <c r="C157" s="101"/>
+      <c r="D157" s="101"/>
+      <c r="E157" s="101"/>
+      <c r="F157" s="101"/>
+      <c r="G157" s="101"/>
+      <c r="H157" s="101"/>
+      <c r="I157" s="101"/>
+      <c r="J157" s="101"/>
+      <c r="K157" s="101"/>
     </row>
     <row r="158" spans="1:11">
-      <c r="A158" s="99"/>
-      <c r="B158" s="100"/>
-      <c r="C158" s="100"/>
-      <c r="D158" s="100"/>
-      <c r="E158" s="100"/>
-      <c r="F158" s="100"/>
-      <c r="G158" s="100"/>
-      <c r="H158" s="100"/>
-      <c r="I158" s="100"/>
-      <c r="J158" s="100"/>
-      <c r="K158" s="100"/>
+      <c r="A158" s="100"/>
+      <c r="B158" s="101"/>
+      <c r="C158" s="101"/>
+      <c r="D158" s="101"/>
+      <c r="E158" s="101"/>
+      <c r="F158" s="101"/>
+      <c r="G158" s="101"/>
+      <c r="H158" s="101"/>
+      <c r="I158" s="101"/>
+      <c r="J158" s="101"/>
+      <c r="K158" s="101"/>
     </row>
     <row r="159" spans="1:11">
-      <c r="A159" s="99"/>
-      <c r="B159" s="100"/>
-      <c r="C159" s="100"/>
-      <c r="D159" s="100"/>
-      <c r="E159" s="100"/>
-      <c r="F159" s="100"/>
-      <c r="G159" s="100"/>
-      <c r="H159" s="100"/>
-      <c r="I159" s="100"/>
-      <c r="J159" s="100"/>
-      <c r="K159" s="100"/>
+      <c r="A159" s="100"/>
+      <c r="B159" s="101"/>
+      <c r="C159" s="101"/>
+      <c r="D159" s="101"/>
+      <c r="E159" s="101"/>
+      <c r="F159" s="101"/>
+      <c r="G159" s="101"/>
+      <c r="H159" s="101"/>
+      <c r="I159" s="101"/>
+      <c r="J159" s="101"/>
+      <c r="K159" s="101"/>
     </row>
     <row r="160" spans="1:11">
-      <c r="A160" s="99"/>
-      <c r="B160" s="100"/>
-      <c r="C160" s="100"/>
-      <c r="D160" s="100"/>
-      <c r="E160" s="100"/>
-      <c r="F160" s="100"/>
-      <c r="G160" s="100"/>
-      <c r="H160" s="100"/>
-      <c r="I160" s="100"/>
-      <c r="J160" s="100"/>
-      <c r="K160" s="100"/>
+      <c r="A160" s="100"/>
+      <c r="B160" s="101"/>
+      <c r="C160" s="101"/>
+      <c r="D160" s="101"/>
+      <c r="E160" s="101"/>
+      <c r="F160" s="101"/>
+      <c r="G160" s="101"/>
+      <c r="H160" s="101"/>
+      <c r="I160" s="101"/>
+      <c r="J160" s="101"/>
+      <c r="K160" s="101"/>
     </row>
     <row r="161" spans="1:11">
-      <c r="A161" s="99"/>
-      <c r="B161" s="100"/>
-      <c r="C161" s="100"/>
-      <c r="D161" s="100"/>
-      <c r="E161" s="100"/>
-      <c r="F161" s="100"/>
-      <c r="G161" s="100"/>
-      <c r="H161" s="100"/>
-      <c r="I161" s="100"/>
-      <c r="J161" s="100"/>
-      <c r="K161" s="100"/>
+      <c r="A161" s="100"/>
+      <c r="B161" s="101"/>
+      <c r="C161" s="101"/>
+      <c r="D161" s="101"/>
+      <c r="E161" s="101"/>
+      <c r="F161" s="101"/>
+      <c r="G161" s="101"/>
+      <c r="H161" s="101"/>
+      <c r="I161" s="101"/>
+      <c r="J161" s="101"/>
+      <c r="K161" s="101"/>
     </row>
     <row r="162" spans="1:11">
-      <c r="A162" s="99"/>
-      <c r="B162" s="100"/>
-      <c r="C162" s="100"/>
-      <c r="D162" s="100"/>
-      <c r="E162" s="100"/>
-      <c r="F162" s="100"/>
-      <c r="G162" s="100"/>
-      <c r="H162" s="100"/>
-      <c r="I162" s="100"/>
-      <c r="J162" s="100"/>
-      <c r="K162" s="100"/>
+      <c r="A162" s="100"/>
+      <c r="B162" s="101"/>
+      <c r="C162" s="101"/>
+      <c r="D162" s="101"/>
+      <c r="E162" s="101"/>
+      <c r="F162" s="101"/>
+      <c r="G162" s="101"/>
+      <c r="H162" s="101"/>
+      <c r="I162" s="101"/>
+      <c r="J162" s="101"/>
+      <c r="K162" s="101"/>
     </row>
     <row r="163" spans="1:11">
-      <c r="A163" s="99"/>
-      <c r="B163" s="100"/>
-      <c r="C163" s="100"/>
-      <c r="D163" s="100"/>
-      <c r="E163" s="100"/>
-      <c r="F163" s="100"/>
-      <c r="G163" s="100"/>
-      <c r="H163" s="100"/>
-      <c r="I163" s="100"/>
-      <c r="J163" s="100"/>
-      <c r="K163" s="100"/>
+      <c r="A163" s="100"/>
+      <c r="B163" s="101"/>
+      <c r="C163" s="101"/>
+      <c r="D163" s="101"/>
+      <c r="E163" s="101"/>
+      <c r="F163" s="101"/>
+      <c r="G163" s="101"/>
+      <c r="H163" s="101"/>
+      <c r="I163" s="101"/>
+      <c r="J163" s="101"/>
+      <c r="K163" s="101"/>
     </row>
     <row r="164" spans="1:11">
       <c r="A164" s="46"/>
@@ -39987,7 +40090,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D18B464F-F54C-4549-BDD7-16317A5143B1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C8FAE45-8EDE-4331-B600-2E7DF703A0C7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
